--- a/artfynd/A 11039-2025 artfynd.xlsx
+++ b/artfynd/A 11039-2025 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rostedt</t>
+          <t>Elin Rostedt, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 11039-2025 artfynd.xlsx
+++ b/artfynd/A 11039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127592917</v>
       </c>
       <c r="B2" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11039-2025 artfynd.xlsx
+++ b/artfynd/A 11039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127592917</v>
       </c>
       <c r="B2" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11039-2025 artfynd.xlsx
+++ b/artfynd/A 11039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127592917</v>
       </c>
       <c r="B2" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11039-2025 artfynd.xlsx
+++ b/artfynd/A 11039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127592917</v>
       </c>
       <c r="B2" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11039-2025 artfynd.xlsx
+++ b/artfynd/A 11039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127592917</v>
       </c>
       <c r="B2" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11039-2025 artfynd.xlsx
+++ b/artfynd/A 11039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127592917</v>
       </c>
       <c r="B2" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11039-2025 artfynd.xlsx
+++ b/artfynd/A 11039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127592917</v>
       </c>
       <c r="B2" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Rostedt, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elin Rostedt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
